--- a/4 курс/8 Управление программными проектами/Экономика.xlsx
+++ b/4 курс/8 Управление программными проектами/Экономика.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grish\OneDrive\Документы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_ЧГУ\4 курс\8 Управление программными проектами\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF5CBF4-BCF0-43EA-A478-23E08C9EFD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5F5E353-B424-45A7-999C-24D9227F7FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{403B308D-25E0-4C34-B0BF-4688826DBE6E}"/>
   </bookViews>
@@ -61,9 +61,6 @@
     <t>Ставка почасовая</t>
   </si>
   <si>
-    <t>Фонд рабочего времени</t>
-  </si>
-  <si>
     <t>Фонд рабочего времени в месяц</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>Годовой экономический эффект</t>
+  </si>
+  <si>
+    <t>Суммарная ЗП</t>
   </si>
 </sst>
 </file>
@@ -276,7 +276,27 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="41">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -925,31 +945,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{91F458C7-1390-4040-A632-E2F0760E6EEE}" name="Таблица2" displayName="Таблица2" ref="A1:L4" totalsRowCount="1" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{91F458C7-1390-4040-A632-E2F0760E6EEE}" name="Таблица2" displayName="Таблица2" ref="A1:L4" totalsRowCount="1" headerRowDxfId="40">
   <autoFilter ref="A1:L3" xr:uid="{91F458C7-1390-4040-A632-E2F0760E6EEE}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{EA131739-A41B-4457-A8DB-7844327B0159}" name="Статья" totalsRowLabel="Итог"/>
-    <tableColumn id="2" xr3:uid="{A9D69DDF-5218-45EC-9470-364146A79762}" name="Ставка" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{9562E679-F26D-41D6-A971-4849A1A2D1FA}" name="Дней в неделю" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{3262A96F-3FAB-4A62-8D45-1CA6AE7EC5A0}" name="Часов в день" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{5E4249DE-502B-430C-B9CF-004DDF22DE57}" name="Месяцев" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{6DE2389D-4592-4F2E-9E98-F9BED32F9D18}" name="Недель" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{BE017F2C-4226-4B3B-AF92-9386221A85C6}" name="Фонд рабочего времени в месяц" dataDxfId="32">
+    <tableColumn id="2" xr3:uid="{A9D69DDF-5218-45EC-9470-364146A79762}" name="Ставка" totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{9562E679-F26D-41D6-A971-4849A1A2D1FA}" name="Дней в неделю" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{3262A96F-3FAB-4A62-8D45-1CA6AE7EC5A0}" name="Часов в день" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{5E4249DE-502B-430C-B9CF-004DDF22DE57}" name="Месяцев" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{6DE2389D-4592-4F2E-9E98-F9BED32F9D18}" name="Недель" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{BE017F2C-4226-4B3B-AF92-9386221A85C6}" name="Фонд рабочего времени в месяц" dataDxfId="33">
       <calculatedColumnFormula>Таблица2[[#This Row],[Недель]] * Таблица2[[#This Row],[Дней в неделю]] * Таблица2[[#This Row],[Часов в день]] / Таблица2[[#This Row],[Месяцев]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{110A9845-8344-4DA5-82EB-889E960EE1D8}" name="Ставка почасовая" totalsRowFunction="sum" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="8" xr3:uid="{110A9845-8344-4DA5-82EB-889E960EE1D8}" name="Ставка почасовая" totalsRowFunction="sum" dataDxfId="32" totalsRowDxfId="31">
       <calculatedColumnFormula xml:space="preserve"> Таблица2[[#This Row],[Ставка]]/Таблица2[[#This Row],[Фонд рабочего времени в месяц]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{26A5FFF6-C163-4651-AD40-2E57FF5CB948}" name="Дополнительная почасовая" totalsRowFunction="sum" dataDxfId="29" totalsRowDxfId="28">
+    <tableColumn id="9" xr3:uid="{26A5FFF6-C163-4651-AD40-2E57FF5CB948}" name="Дополнительная почасовая" totalsRowFunction="sum" dataDxfId="30" totalsRowDxfId="29">
       <calculatedColumnFormula>Таблица2[[#This Row],[Ставка почасовая]] * 0.1 * Таблица2[[#This Row],[Ставка почасовая]] / 100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{0CD7703D-D82D-4497-892E-3743F6C8B325}" name="Общая почасовая" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="10" xr3:uid="{0CD7703D-D82D-4497-892E-3743F6C8B325}" name="Общая почасовая" totalsRowFunction="sum" dataDxfId="28" totalsRowDxfId="27">
       <calculatedColumnFormula xml:space="preserve"> Таблица2[[#This Row],[Ставка почасовая]]+Таблица2[[#This Row],[Дополнительная почасовая]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{6BB0D846-A8FF-4BB7-AD64-E2127BA3D9C3}" name="Отчисления" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24">
+    <tableColumn id="11" xr3:uid="{6BB0D846-A8FF-4BB7-AD64-E2127BA3D9C3}" name="Отчисления" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>Таблица2[[#This Row],[Общая почасовая]]*0.3</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{440564A9-1052-454D-83F6-6175CBBB3490}" name="Зарплата" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22">
+    <tableColumn id="12" xr3:uid="{440564A9-1052-454D-83F6-6175CBBB3490}" name="Зарплата" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="23">
       <calculatedColumnFormula>(Таблица2[[#This Row],[Общая почасовая]]+Таблица2[[#This Row],[Отчисления]])*Таблица2[[#This Row],[Фонд рабочего времени в месяц]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -958,57 +978,60 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8F2C8FBE-D3E0-4BF7-BC16-2F5EC901E524}" name="Таблица3" displayName="Таблица3" ref="A1:V2" totalsRowShown="0" headerRowDxfId="21">
-  <autoFilter ref="A1:V2" xr:uid="{8F2C8FBE-D3E0-4BF7-BC16-2F5EC901E524}"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8F2C8FBE-D3E0-4BF7-BC16-2F5EC901E524}" name="Таблица3" displayName="Таблица3" ref="A1:W2" totalsRowShown="0" headerRowDxfId="22">
+  <autoFilter ref="A1:W2" xr:uid="{8F2C8FBE-D3E0-4BF7-BC16-2F5EC901E524}"/>
+  <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{CBC423E0-F499-4DDA-A55D-ED8722436BC6}" name="Машина"/>
-    <tableColumn id="2" xr3:uid="{CDE22FDA-BA8D-402E-AE64-54354C7BCD02}" name="Мощность (квт)" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{5A2409DD-4BA1-484B-B799-884DF03FEE91}" name="Стоимость 1квт/ч" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{EBA84123-F3C4-4723-9F7B-2C890B6D37DC}" name="Стоимость" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{9B5E1E06-6141-442C-868E-B5F23CDC93FF}" name="Срок службы, лет" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{8B0D482B-5D89-4AEF-80E9-2216BA2A23AA}" name="Часов в день" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{C5B788CE-03D6-49BD-9802-1F27CC704EAF}" name="Дней в году" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{BB9DCEBD-3848-4DD2-9202-58335ED32BE7}" name="Часов в год" dataDxfId="14">
+    <tableColumn id="2" xr3:uid="{CDE22FDA-BA8D-402E-AE64-54354C7BCD02}" name="Мощность (квт)" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{5A2409DD-4BA1-484B-B799-884DF03FEE91}" name="Стоимость 1квт/ч" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{EBA84123-F3C4-4723-9F7B-2C890B6D37DC}" name="Стоимость" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{9B5E1E06-6141-442C-868E-B5F23CDC93FF}" name="Срок службы, лет" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{8B0D482B-5D89-4AEF-80E9-2216BA2A23AA}" name="Часов в день" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{C5B788CE-03D6-49BD-9802-1F27CC704EAF}" name="Дней в году" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{BB9DCEBD-3848-4DD2-9202-58335ED32BE7}" name="Часов в год" dataDxfId="15">
       <calculatedColumnFormula>Таблица3[[#This Row],[Дней в году]]*Таблица3[[#This Row],[Часов в день]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{347BC2DF-EEB6-43D9-BFF7-2964698768E9}" name="Стоимость машингого времени, руб/ч" dataDxfId="13">
+    <tableColumn id="9" xr3:uid="{347BC2DF-EEB6-43D9-BFF7-2964698768E9}" name="Стоимость машингого времени, руб/ч" dataDxfId="14">
       <calculatedColumnFormula>Таблица3[[#This Row],[Стоимость]]/(Таблица3[[#This Row],[Дней в году]]*Таблица3[[#This Row],[Часов в день]]*Таблица3[[#This Row],[Срок службы, лет]])+ Таблица3[[#This Row],[Мощность (квт)]] * Таблица3[[#This Row],[Стоимость 1квт/ч]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BE204BB7-EC39-4DC3-A85F-9EA415005D98}" name="Затраты на использование машинного времени" dataDxfId="12">
+    <tableColumn id="10" xr3:uid="{BE204BB7-EC39-4DC3-A85F-9EA415005D98}" name="Затраты на использование машинного времени" dataDxfId="13">
       <calculatedColumnFormula>Таблица3[[#This Row],[Стоимость машингого времени, руб/ч]]*Таблица3[[#This Row],[Часов в год]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{2837F8CC-98EA-42AD-BE43-01B5267D3AE8}" name="Затраты на носители" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{2837F8CC-98EA-42AD-BE43-01B5267D3AE8}" name="Затраты на носители" dataDxfId="12">
       <calculatedColumnFormula>0.02 * Таблица3[[#This Row],[Стоимость]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{1D0170BD-D883-448F-B349-AEAEDBD28793}" name="Профилактика" dataDxfId="10">
+    <tableColumn id="12" xr3:uid="{1D0170BD-D883-448F-B349-AEAEDBD28793}" name="Профилактика" dataDxfId="11">
       <calculatedColumnFormula>0.04*Таблица3[[#This Row],[Стоимость]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{B1431A1E-A853-46E6-99BA-F3A8612990C0}" name="Затраты на помещение" dataDxfId="9">
+    <tableColumn id="13" xr3:uid="{B1431A1E-A853-46E6-99BA-F3A8612990C0}" name="Затраты на помещение" dataDxfId="10">
       <calculatedColumnFormula>20000 * 0.1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{5E89EC06-2C7C-425B-9FD4-609953EC6766}" name="Себестоимость разработки программного продукта" dataDxfId="8">
-      <calculatedColumnFormula>336213.71+Таблица3[[#This Row],[Затраты на использование машинного времени]]*4/12+Таблица3[[#This Row],[Затраты на носители]]+Таблица3[[#This Row],[Профилактика]]+Таблица3[[#This Row],[Затраты на помещение]]*4</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="15" xr3:uid="{B982FE17-88E5-4B1C-B87B-B698A11B6765}" name="Минимальная цена ПП" dataDxfId="7">
+    <tableColumn id="23" xr3:uid="{C5B059E8-B3E7-490E-98CE-54C13AFCCEF7}" name="Суммарная ЗП" dataDxfId="0">
+      <calculatedColumnFormula>336213.71</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{5E89EC06-2C7C-425B-9FD4-609953EC6766}" name="Себестоимость разработки программного продукта" dataDxfId="9">
+      <calculatedColumnFormula>Таблица3[[#This Row],[Суммарная ЗП]]+Таблица3[[#This Row],[Затраты на использование машинного времени]]*4/12+Таблица3[[#This Row],[Затраты на носители]]+Таблица3[[#This Row],[Профилактика]]+Таблица3[[#This Row],[Затраты на помещение]]*4</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{B982FE17-88E5-4B1C-B87B-B698A11B6765}" name="Минимальная цена ПП" dataDxfId="8">
       <calculatedColumnFormula>Таблица3[[#This Row],[Себестоимость разработки программного продукта]]*1.2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{68F3FCBE-C336-43A9-82CA-D796B5B71524}" name="Объём машинного времени в течение года, часов" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{F2063422-FF65-4933-8D71-A2AD81730781}" name="Расходы" dataDxfId="5">
+    <tableColumn id="16" xr3:uid="{68F3FCBE-C336-43A9-82CA-D796B5B71524}" name="Объём машинного времени в течение года, часов" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{F2063422-FF65-4933-8D71-A2AD81730781}" name="Расходы" dataDxfId="6">
       <calculatedColumnFormula>Таблица3[[#This Row],[Объём машинного времени в течение года, часов]] * 10.28  + Таблица3[[#This Row],[Минимальная цена ПП]] / 2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{0FD78D4B-1333-4D97-A9C5-4940E5D82829}" name="Капитальные" dataDxfId="4">
+    <tableColumn id="18" xr3:uid="{0FD78D4B-1333-4D97-A9C5-4940E5D82829}" name="Капитальные" dataDxfId="5">
       <calculatedColumnFormula>Таблица3[[#This Row],[Объём машинного времени в течение года, часов]]*80000 / 2000 + Таблица3[[#This Row],[Минимальная цена ПП]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4D848631-368F-4A98-AD80-3403AEDC9B19}" name="Затраты вручную" dataDxfId="3">
-      <calculatedColumnFormula>1.21 * 120000 * 12</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="20" xr3:uid="{9540ED02-B76C-4138-94B2-6B035E0963E8}" name="Годовая экономия" dataDxfId="2">
+    <tableColumn id="19" xr3:uid="{4D848631-368F-4A98-AD80-3403AEDC9B19}" name="Затраты вручную" dataDxfId="4">
+      <calculatedColumnFormula>1.21 * 120000 * 12 / 3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{9540ED02-B76C-4138-94B2-6B035E0963E8}" name="Годовая экономия" dataDxfId="3">
       <calculatedColumnFormula>Таблица3[[#This Row],[Затраты вручную]]-Таблица3[[#This Row],[Расходы]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{AE41AC12-AF26-40F8-8810-7E3C92640AF9}" name="Срок окурамеости" dataDxfId="1">
+    <tableColumn id="21" xr3:uid="{AE41AC12-AF26-40F8-8810-7E3C92640AF9}" name="Срок окурамеости" dataDxfId="2">
       <calculatedColumnFormula>Таблица3[[#This Row],[Капитальные]]/Таблица3[[#This Row],[Годовая экономия]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{905F52A8-8CE1-4986-B4D0-C70A1777E747}" name="Годовой экономический эффект" dataDxfId="0">
+    <tableColumn id="22" xr3:uid="{905F52A8-8CE1-4986-B4D0-C70A1777E747}" name="Годовой экономический эффект" dataDxfId="1">
       <calculatedColumnFormula>Таблица3[[#This Row],[Годовая экономия]]-0.15*Таблица3[[#This Row],[Капитальные]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1358,34 +1381,34 @@
         <v>3</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1478,7 +1501,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
         <f>SUBTOTAL(109,Таблица2[Ставка])</f>
@@ -1567,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB76C24D-DBAD-4BC5-A88E-07401D3654F5}">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
@@ -1583,88 +1606,92 @@
     <col min="11" max="11" width="15.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5546875" customWidth="1"/>
-    <col min="17" max="17" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5546875" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>24</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>0.3</v>
@@ -1705,46 +1732,50 @@
         <v>3200</v>
       </c>
       <c r="M2" s="11">
-        <f t="shared" ref="M2:M3" si="0">20000 * 0.1</f>
+        <f t="shared" ref="M2" si="0">20000 * 0.1</f>
         <v>2000</v>
       </c>
       <c r="N2" s="10">
-        <f>336213.71+Таблица3[[#This Row],[Затраты на использование машинного времени]]*4/12+Таблица3[[#This Row],[Затраты на носители]]+Таблица3[[#This Row],[Профилактика]]+Таблица3[[#This Row],[Затраты на помещение]]*4</f>
+        <f>336213.71</f>
+        <v>336213.71</v>
+      </c>
+      <c r="O2" s="10">
+        <f>Таблица3[[#This Row],[Суммарная ЗП]]+Таблица3[[#This Row],[Затраты на использование машинного времени]]*4/12+Таблица3[[#This Row],[Затраты на носители]]+Таблица3[[#This Row],[Профилактика]]+Таблица3[[#This Row],[Затраты на помещение]]*4</f>
         <v>355785.57133333338</v>
       </c>
-      <c r="O2" s="10">
+      <c r="P2" s="10">
         <f>Таблица3[[#This Row],[Себестоимость разработки программного продукта]]*1.2</f>
         <v>426942.68560000003</v>
       </c>
-      <c r="P2" s="10">
+      <c r="Q2" s="10">
         <v>2964</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="R2" s="10">
         <f>Таблица3[[#This Row],[Объём машинного времени в течение года, часов]] * 10.28  + Таблица3[[#This Row],[Минимальная цена ПП]] / 2</f>
         <v>243941.26280000003</v>
       </c>
-      <c r="R2" s="10">
+      <c r="S2" s="10">
         <f>Таблица3[[#This Row],[Объём машинного времени в течение года, часов]]*80000 / 2000 + Таблица3[[#This Row],[Минимальная цена ПП]]</f>
         <v>545502.68559999997</v>
       </c>
-      <c r="S2" s="10">
-        <f>1.21 * 120000 * 12</f>
-        <v>1742400</v>
-      </c>
       <c r="T2" s="10">
+        <f>1.21 * 120000 * 12 / 3</f>
+        <v>580800</v>
+      </c>
+      <c r="U2" s="10">
         <f>Таблица3[[#This Row],[Затраты вручную]]-Таблица3[[#This Row],[Расходы]]</f>
-        <v>1498458.7371999999</v>
-      </c>
-      <c r="U2" s="10">
+        <v>336858.73719999997</v>
+      </c>
+      <c r="V2" s="10">
         <f>Таблица3[[#This Row],[Капитальные]]/Таблица3[[#This Row],[Годовая экономия]]</f>
-        <v>0.36404251385615</v>
-      </c>
-      <c r="V2" s="10">
+        <v>1.619381139210659</v>
+      </c>
+      <c r="W2" s="10">
         <f>Таблица3[[#This Row],[Годовая экономия]]-0.15*Таблица3[[#This Row],[Капитальные]]</f>
-        <v>1416633.3343599997</v>
+        <v>255033.33435999998</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
